--- a/projects/_DefaultProject.xlsx
+++ b/projects/_DefaultProject.xlsx
@@ -50,7 +50,7 @@
     <x:t>UpdatedAt</x:t>
   </x:si>
   <x:si>
-    <x:t>2026/9/2 19:58:21</x:t>
+    <x:t>2026/9/3 8:53:06</x:t>
   </x:si>
   <x:si>
     <x:t>Remark</x:t>
